--- a/experiment_results/combined_sweep/rtt_bursts_S4_atk5pct_wu500000.xlsx
+++ b/experiment_results/combined_sweep/rtt_bursts_S4_atk5pct_wu500000.xlsx
@@ -491,7 +491,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>1.48</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -548,12 +548,12 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>0.93</t>
+          <t>0.87</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -605,12 +605,12 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>1.27</t>
+          <t>1.24</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>0.34</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -630,7 +630,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>407909</t>
+          <t>230015</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -662,7 +662,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.61</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -687,7 +687,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>478565</t>
+          <t>248588</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -719,12 +719,12 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>0.60</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>0.01</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -744,7 +744,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>553760</t>
+          <t>305211</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -781,7 +781,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>0.18</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -801,7 +801,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>671809</t>
+          <t>366637</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -858,7 +858,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>785773</t>
+          <t>419175</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -890,12 +890,12 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -915,7 +915,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>879356</t>
+          <t>460221</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -947,12 +947,12 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>1.01</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>0.05</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -972,7 +972,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>949004</t>
+          <t>488823</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1004,12 +1004,12 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>1.02</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.01</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -1029,7 +1029,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>1003676</t>
+          <t>514893</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1061,12 +1061,12 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>1.26</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>0.24</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>1049604</t>
+          <t>534751</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1118,12 +1118,12 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>0.03</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -1143,7 +1143,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>1104580</t>
+          <t>569869</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1175,12 +1175,12 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>1.24</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>0.05</t>
+          <t>0.04</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -1200,7 +1200,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>1173803</t>
+          <t>603973</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.86</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -1257,7 +1257,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>1249160</t>
+          <t>645226</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1289,12 +1289,12 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>0.93</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.07</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -1314,7 +1314,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>1337464</t>
+          <t>692278</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1346,12 +1346,12 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>0.89</t>
+          <t>0.65</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>0.36</t>
+          <t>0.28</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>1381975</t>
+          <t>689737</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
@@ -1403,12 +1403,12 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>0.44</t>
+          <t>0.23</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>0.42</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
@@ -1428,7 +1428,7 @@
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>1372683</t>
+          <t>682986</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
@@ -1460,12 +1460,12 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>0.17</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>0.06</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1485,7 +1485,7 @@
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>1365947</t>
+          <t>683001</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
@@ -1517,12 +1517,12 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>0.37</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.20</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1542,7 +1542,7 @@
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>1365962</t>
+          <t>683001</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
